--- a/backend/data/financials_by_company/1123.HK.xlsx
+++ b/backend/data/financials_by_company/1123.HK.xlsx
@@ -3916,7 +3916,7 @@
         <v>-759000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>-0.033</v>
@@ -4177,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
